--- a/data/rateBuildUp/RebateRefreshOutput/RBU_Execution_Summary27JulPROD.xlsx
+++ b/data/rateBuildUp/RebateRefreshOutput/RBU_Execution_Summary27JulPROD.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +488,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -504,7 +504,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>188</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>178</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -677,7 +677,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>371</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>265</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -758,7 +758,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -771,10 +771,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -812,7 +812,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -839,7 +839,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -866,7 +866,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>571</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
